--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260616.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260616.xlsx
@@ -733,17 +733,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>6,117,074</t>
+          <t>33,023,117</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -755,17 +755,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>33,023,117</t>
+          <t>6,117,074</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>14,527,380</t>
+          <t>326,505,235</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>326,505,235</t>
+          <t>14,527,380</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>336,060,402</t>
+          <t>7,322,530</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>7,322,530</t>
+          <t>336,060,402</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,204,837</t>
+          <t>104,750,086</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>104,750,086</t>
+          <t>1,204,837</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>230,840,278</t>
+          <t>1,687,563</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,687,563</t>
+          <t>230,840,278</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202607NYF</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>台灣50ETF股票期貨</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,738</t>
+          <t>20,448,098</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>202607NYF</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>台灣50ETF股票期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>20,448,098</t>
+          <t>1,738</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
